--- a/output/central_unit_requests/CIandS - end-2026 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIandS - end-2026 sustainability reporting request.xlsx
@@ -2166,7 +2166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E9"/>
+  <dimension ref="B1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2190,6 +2190,21 @@
           <t>Y/N</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Target status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Response count</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="B2" t="inlineStr">
@@ -2212,6 +2227,17 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -2234,6 +2260,17 @@
           <t>No</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -2256,6 +2293,17 @@
           <t>TBC</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Not met</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -2267,6 +2315,17 @@
         <is>
           <t>Support meeting</t>
         </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Not yet started</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">

--- a/output/central_unit_requests/CIandS - end-2026 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIandS - end-2026 sustainability reporting request.xlsx
@@ -908,7 +908,7 @@
       </c>
       <c r="G16" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Climate leadership section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will report the University's climate-change resilience maturity rating, key gaps and priority actions in the 2026 Sustainability Report (building on the Climate Change Preparedness Framework assessment reported in 2025).</t>
         </is>
       </c>
       <c r="H16" s="19" t="inlineStr"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="G17" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Estate and infrastructure section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will use case study evidence to show how sustainability maturity is increasing in estate and infrastructure planning, development and operations in the 2026 Sustainability Report.</t>
         </is>
       </c>
       <c r="H17" s="19" t="inlineStr"/>
@@ -994,7 +994,7 @@
       </c>
       <c r="G18" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Estate and infrastructure section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will use estimated sustainability impacts of the capital plan to inform progress reporting towards the emissions reduction target and other priority areas (to the extent information is available).</t>
         </is>
       </c>
       <c r="H18" s="19" t="inlineStr"/>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="G19" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Estate and infrastructure section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will report on sustainability activities and impacts of major estate and infrastructure projects and programs in the Estate and infrastructure section of the 2026 Sustainability Report.</t>
         </is>
       </c>
       <c r="H19" s="19" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G20" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Estate and infrastructure section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will report on how Indigenous approaches to sustainability are informing estate planning and development, with examples where permission to share is confirmed.</t>
         </is>
       </c>
       <c r="H20" s="19" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="G28" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Exceptional education section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will collate examples of innovative sustainability teaching and learning across faculties to inform the Exceptional education section of the 2026 Sustainability Report, and select one or two for short case studies.</t>
         </is>
       </c>
       <c r="H28" s="19" t="inlineStr"/>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="G29" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Exceptional education section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>This is a new indicator. We will use responses to establish a baseline of how (and whether) faculties are understanding student sustainability self-efficacy, and report on early pilots in the 2026 Sustainability Report. A nil response is useful to us.</t>
         </is>
       </c>
       <c r="H29" s="19" t="inlineStr"/>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="G30" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Exceptional education section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will combine faculty examples with central Wattle Fellowship and Melbourne Plus data to report on the range and reach of sustainability-focused experiential and co-curricular learning across the University.</t>
         </is>
       </c>
       <c r="H30" s="19" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G31" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Exceptional education section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will use nominated alumni to develop short graduate profiles for the 2026 Sustainability Report (subject to consent), and record any faculty approaches to tracking graduate outcomes to inform how this indicator is measured from 2027.</t>
         </is>
       </c>
       <c r="H31" s="19" t="inlineStr"/>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="G32" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Transformational research section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will report on examples of researchers helping solve the University's own operational sustainability challenges, alongside CLLAP projects reported by CI&amp;S, and share them with operational teams to identify further collaboration.</t>
         </is>
       </c>
       <c r="H32" s="19" t="inlineStr"/>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="G33" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Transformational research section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will select the strongest examples to develop as full research case studies for the 2026 Sustainability Report (we may contact you for more detail and images).</t>
         </is>
       </c>
       <c r="H33" s="19" t="inlineStr"/>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="G34" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Transformational research section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will report on how sustainability is being built into research systems and support across the University, and use responses to establish a baseline for this new target.</t>
         </is>
       </c>
       <c r="H34" s="19" t="inlineStr"/>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="G35" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Transformational research section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
         </is>
       </c>
       <c r="H35" s="19" t="inlineStr"/>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G36" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Climate leadership section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>For internal planning: we will record the status of the planned review of Climate Leadership targets (due by 2030).</t>
         </is>
       </c>
       <c r="H36" s="19" t="inlineStr"/>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="G37" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Climate leadership section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will use these examples to show how the University communicates climate research and learning to external audiences, and as an input to the institutional decarbonisation research and education mapping due by 2028.</t>
         </is>
       </c>
       <c r="H37" s="19" t="inlineStr"/>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="G38" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Responsible AI section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will provide a high-level overview of AI's estimated operational impacts and opportunities in 2026, ahead of more detailed measurement from 2027.</t>
         </is>
       </c>
       <c r="H38" s="19" t="inlineStr"/>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="G39" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Responsible AI section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will select examples of sustainability and AI-related education, research and collaboration as case studies for the new Responsible AI section of the 2026 Sustainability Report.</t>
         </is>
       </c>
       <c r="H39" s="19" t="inlineStr"/>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="G40" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Modern slavery and human rights section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will draw on the annual Modern Slavery Statement and case studies to report on the University's approach to modern slavery and human rights risks (timing to be aligned with the Statement).</t>
         </is>
       </c>
       <c r="H40" s="19" t="inlineStr"/>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="G41" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Responsible investments section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will report on sustainability-related investment portfolio metrics and the University's compliance with related obligations (e.g. UNPRI) in the Responsible investments section of the 2026 Sustainability Report.</t>
         </is>
       </c>
       <c r="H41" s="19" t="inlineStr"/>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="G42" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Enablers section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will share examples of living labs from across the University in the 2026 Sustainability Report, alongside CLLAP projects reported by CI&amp;S.</t>
         </is>
       </c>
       <c r="H42" s="19" t="inlineStr"/>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G43" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Enablers section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
       <c r="H43" s="19" t="inlineStr"/>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="G44" s="19" t="inlineStr">
         <is>
-          <t>We will use this to inform the Enablers section of the 2026 Sustainability Report (transition year), and to establish a baseline for reporting against Sustainability 2030 from 2027. Strong examples may be followed up as case studies.</t>
+          <t>We will report on how sustainability is integrated into governance and decision-making across faculties and portfolios, and use responses as a baseline for the governance enabler from 2027.</t>
         </is>
       </c>
       <c r="H44" s="19" t="inlineStr"/>

--- a/output/central_unit_requests/CIandS - end-2026 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIandS - end-2026 sustainability reporting request.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Reporting template" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. OPTIONAL highlighted stories" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. SR25 responses" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +41,32 @@
       <b val="1"/>
       <color rgb="00002060"/>
       <sz val="22"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -80,12 +107,6 @@
       <sz val="14"/>
     </font>
     <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
       <color rgb="000E2841"/>
@@ -100,11 +121,9 @@
     <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
+      <color rgb="000563C1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <sz val="11"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="7">
@@ -116,7 +135,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="000B3040"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C1E4F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -126,17 +155,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C1E4F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -147,12 +166,6 @@
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
     </border>
     <border>
       <left style="thin">
@@ -168,62 +181,73 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -599,7 +623,7 @@
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col hidden="1" outlineLevel="1" width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col hidden="1" outlineLevel="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" outlineLevel="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" outlineLevel="1" width="24" customWidth="1" min="11" max="11"/>
@@ -650,7 +674,7 @@
 • Provide commentary on progress towards each target (Column M or N)
 • Provide supporting documentation if required (Column O), including links to images
 • Note the source of your information and any limitations (Column P), then confirm the information is accurate (Columns Q–R)
-• Your end-2025 responses (where a related target existed) can be viewed by clicking the [+] icon above Columns H–K
+• Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch.
 • Due: Friday 15 January 2027 (TBC). Questions: Sustainability Strategy team (sustainability-strategy@unimelb.edu.au – TBC)</t>
@@ -728,7 +752,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>End-2025 reporting (for reference – click [+] above to expand)</t>
+          <t>End-2025 reporting (click the ref to see your full SR25 response; [+] above expands a summary)</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
@@ -903,7 +927,8 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>Provide update of University maturity assesment. Include maturity ratings, key gaps and priority improvement actions.when available</t>
+          <t>We did not receive an end-2025 response for the related SP2030 target 8a(i), so please include any relevant activity from across 2026.
+Provide update of University maturity assesment. Include maturity ratings, key gaps and priority improvement actions.when available</t>
         </is>
       </c>
       <c r="G16" s="19" t="inlineStr">
@@ -911,8 +936,17 @@
           <t>We will report the University's climate-change resilience maturity rating, key gaps and priority actions in the 2026 Sustainability Report (building on the Climate Change Preparedness Framework assessment reported in 2025).</t>
         </is>
       </c>
-      <c r="H16" s="19" t="inlineStr"/>
-      <c r="I16" s="19" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>8a(i)
+→ view SR25 response</t>
+        </is>
+      </c>
+      <c r="I16" s="19" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
       <c r="J16" s="19" t="inlineStr"/>
       <c r="K16" s="19" t="inlineStr"/>
       <c r="L16" s="19" t="n"/>
@@ -946,7 +980,8 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>Case study evidence of increased sustainability maturity in estate and infrastructure planning, development and operations, could include examples of changes to standards, processes, governance, decision-making or project requirements that support Sustainability 2030 priority areas.</t>
+          <t>We did not receive an end-2025 response for the related SP2030 target 7b, so please include any relevant activity from across 2026.
+Case study evidence of increased sustainability maturity in estate and infrastructure planning, development and operations, could include examples of changes to standards, processes, governance, decision-making or project requirements that support Sustainability 2030 priority areas.</t>
         </is>
       </c>
       <c r="G17" s="19" t="inlineStr">
@@ -954,7 +989,12 @@
           <t>We will use case study evidence to show how sustainability maturity is increasing in estate and infrastructure planning, development and operations in the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H17" s="19" t="inlineStr"/>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>7b
+→ view SR25 response</t>
+        </is>
+      </c>
       <c r="I17" s="19" t="inlineStr"/>
       <c r="J17" s="19" t="inlineStr"/>
       <c r="K17" s="19" t="inlineStr"/>
@@ -997,7 +1037,11 @@
           <t>We will use estimated sustainability impacts of the capital plan to inform progress reporting towards the emissions reduction target and other priority areas (to the extent information is available).</t>
         </is>
       </c>
-      <c r="H18" s="19" t="inlineStr"/>
+      <c r="H18" s="19" t="inlineStr">
+        <is>
+          <t>N/A – new indicator</t>
+        </is>
+      </c>
       <c r="I18" s="19" t="inlineStr"/>
       <c r="J18" s="19" t="inlineStr"/>
       <c r="K18" s="19" t="inlineStr"/>
@@ -1040,7 +1084,11 @@
           <t>We will report on sustainability activities and impacts of major estate and infrastructure projects and programs in the Estate and infrastructure section of the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H19" s="19" t="inlineStr"/>
+      <c r="H19" s="19" t="inlineStr">
+        <is>
+          <t>N/A – new indicator</t>
+        </is>
+      </c>
       <c r="I19" s="19" t="inlineStr"/>
       <c r="J19" s="19" t="inlineStr"/>
       <c r="K19" s="19" t="inlineStr"/>
@@ -1083,7 +1131,11 @@
           <t>We will report on how Indigenous approaches to sustainability are informing estate planning and development, with examples where permission to share is confirmed.</t>
         </is>
       </c>
-      <c r="H20" s="19" t="inlineStr"/>
+      <c r="H20" s="19" t="inlineStr">
+        <is>
+          <t>N/A – new indicator</t>
+        </is>
+      </c>
       <c r="I20" s="19" t="inlineStr"/>
       <c r="J20" s="19" t="inlineStr"/>
       <c r="K20" s="19" t="inlineStr"/>
@@ -1110,7 +1162,7 @@
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>End-2025 reporting (for reference – click [+] above to expand)</t>
+          <t>End-2025 reporting (click the ref to see your full SR25 response; [+] above expands a summary)</t>
         </is>
       </c>
       <c r="L25" s="13" t="inlineStr">
@@ -1286,7 +1338,11 @@
           <t>We will collate examples of innovative sustainability teaching and learning across faculties to inform the Exceptional education section of the 2026 Sustainability Report, and select one or two for short case studies.</t>
         </is>
       </c>
-      <c r="H28" s="19" t="inlineStr"/>
+      <c r="H28" s="19" t="inlineStr">
+        <is>
+          <t>N/A – new indicator</t>
+        </is>
+      </c>
       <c r="I28" s="19" t="inlineStr"/>
       <c r="J28" s="19" t="inlineStr"/>
       <c r="K28" s="19" t="inlineStr"/>
@@ -1329,7 +1385,11 @@
           <t>This is a new indicator. We will use responses to establish a baseline of how (and whether) faculties are understanding student sustainability self-efficacy, and report on early pilots in the 2026 Sustainability Report. A nil response is useful to us.</t>
         </is>
       </c>
-      <c r="H29" s="19" t="inlineStr"/>
+      <c r="H29" s="19" t="inlineStr">
+        <is>
+          <t>N/A – new indicator</t>
+        </is>
+      </c>
       <c r="I29" s="19" t="inlineStr"/>
       <c r="J29" s="19" t="inlineStr"/>
       <c r="K29" s="19" t="inlineStr"/>
@@ -1372,7 +1432,11 @@
           <t>We will combine faculty examples with central Wattle Fellowship and Melbourne Plus data to report on the range and reach of sustainability-focused experiential and co-curricular learning across the University.</t>
         </is>
       </c>
-      <c r="H30" s="19" t="inlineStr"/>
+      <c r="H30" s="19" t="inlineStr">
+        <is>
+          <t>N/A – new indicator</t>
+        </is>
+      </c>
       <c r="I30" s="19" t="inlineStr"/>
       <c r="J30" s="19" t="inlineStr"/>
       <c r="K30" s="19" t="inlineStr"/>
@@ -1415,7 +1479,11 @@
           <t>We will use nominated alumni to develop short graduate profiles for the 2026 Sustainability Report (subject to consent), and record any faculty approaches to tracking graduate outcomes to inform how this indicator is measured from 2027.</t>
         </is>
       </c>
-      <c r="H31" s="19" t="inlineStr"/>
+      <c r="H31" s="19" t="inlineStr">
+        <is>
+          <t>N/A – new indicator</t>
+        </is>
+      </c>
       <c r="I31" s="19" t="inlineStr"/>
       <c r="J31" s="19" t="inlineStr"/>
       <c r="K31" s="19" t="inlineStr"/>
@@ -1450,7 +1518,8 @@
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>Please provide examples of researchers within your Faculty/Portfolio contributing to University operational sustainability priorities through partnerships, advisory input, living labs, applied projects or decision-support. Briefly describe the operational challenge, researcher contribution and resulting or expected outcome.</t>
+          <t>In end-2025 reporting your area reported on the related SP2030 target 5a(ii) and rated it 'Partially met' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+Please provide examples of researchers within your Faculty/Portfolio contributing to University operational sustainability priorities through partnerships, advisory input, living labs, applied projects or decision-support. Briefly describe the operational challenge, researcher contribution and resulting or expected outcome.</t>
         </is>
       </c>
       <c r="G32" s="19" t="inlineStr">
@@ -1458,9 +1527,22 @@
           <t>We will report on examples of researchers helping solve the University's own operational sustainability challenges, alongside CLLAP projects reported by CI&amp;S, and share them with operational teams to identify further collaboration.</t>
         </is>
       </c>
-      <c r="H32" s="19" t="inlineStr"/>
-      <c r="I32" s="19" t="inlineStr"/>
-      <c r="J32" s="19" t="inlineStr"/>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>5a(ii)
+→ view SR25 response</t>
+        </is>
+      </c>
+      <c r="I32" s="19" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="J32" s="19" t="inlineStr">
+        <is>
+          <t>Tangible improvement in some areas, but not all (haven't done ASRS, for example).</t>
+        </is>
+      </c>
       <c r="K32" s="19" t="inlineStr"/>
       <c r="L32" s="19" t="n"/>
       <c r="M32" s="19" t="n"/>
@@ -1501,7 +1583,11 @@
           <t>We will select the strongest examples to develop as full research case studies for the 2026 Sustainability Report (we may contact you for more detail and images).</t>
         </is>
       </c>
-      <c r="H33" s="19" t="inlineStr"/>
+      <c r="H33" s="19" t="inlineStr">
+        <is>
+          <t>N/A – new indicator</t>
+        </is>
+      </c>
       <c r="I33" s="19" t="inlineStr"/>
       <c r="J33" s="19" t="inlineStr"/>
       <c r="K33" s="19" t="inlineStr"/>
@@ -1544,7 +1630,11 @@
           <t>We will report on how sustainability is being built into research systems and support across the University, and use responses to establish a baseline for this new target.</t>
         </is>
       </c>
-      <c r="H34" s="19" t="inlineStr"/>
+      <c r="H34" s="19" t="inlineStr">
+        <is>
+          <t>N/A – new indicator</t>
+        </is>
+      </c>
       <c r="I34" s="19" t="inlineStr"/>
       <c r="J34" s="19" t="inlineStr"/>
       <c r="K34" s="19" t="inlineStr"/>
@@ -1587,7 +1677,11 @@
           <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
         </is>
       </c>
-      <c r="H35" s="19" t="inlineStr"/>
+      <c r="H35" s="19" t="inlineStr">
+        <is>
+          <t>N/A – new indicator</t>
+        </is>
+      </c>
       <c r="I35" s="19" t="inlineStr"/>
       <c r="J35" s="19" t="inlineStr"/>
       <c r="K35" s="19" t="inlineStr"/>
@@ -1636,7 +1730,11 @@
           <t>For internal planning: we will record the status of the planned review of Climate Leadership targets (due by 2030).</t>
         </is>
       </c>
-      <c r="H36" s="19" t="inlineStr"/>
+      <c r="H36" s="19" t="inlineStr">
+        <is>
+          <t>N/A – new indicator</t>
+        </is>
+      </c>
       <c r="I36" s="19" t="inlineStr"/>
       <c r="J36" s="19" t="inlineStr"/>
       <c r="K36" s="19" t="inlineStr"/>
@@ -1679,7 +1777,11 @@
           <t>We will use these examples to show how the University communicates climate research and learning to external audiences, and as an input to the institutional decarbonisation research and education mapping due by 2028.</t>
         </is>
       </c>
-      <c r="H37" s="19" t="inlineStr"/>
+      <c r="H37" s="19" t="inlineStr">
+        <is>
+          <t>N/A – new indicator</t>
+        </is>
+      </c>
       <c r="I37" s="19" t="inlineStr"/>
       <c r="J37" s="19" t="inlineStr"/>
       <c r="K37" s="19" t="inlineStr"/>
@@ -1722,7 +1824,11 @@
           <t>We will provide a high-level overview of AI's estimated operational impacts and opportunities in 2026, ahead of more detailed measurement from 2027.</t>
         </is>
       </c>
-      <c r="H38" s="19" t="inlineStr"/>
+      <c r="H38" s="19" t="inlineStr">
+        <is>
+          <t>N/A – new indicator</t>
+        </is>
+      </c>
       <c r="I38" s="19" t="inlineStr"/>
       <c r="J38" s="19" t="inlineStr"/>
       <c r="K38" s="19" t="inlineStr"/>
@@ -1765,7 +1871,11 @@
           <t>We will select examples of sustainability and AI-related education, research and collaboration as case studies for the new Responsible AI section of the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H39" s="19" t="inlineStr"/>
+      <c r="H39" s="19" t="inlineStr">
+        <is>
+          <t>N/A – new indicator</t>
+        </is>
+      </c>
       <c r="I39" s="19" t="inlineStr"/>
       <c r="J39" s="19" t="inlineStr"/>
       <c r="K39" s="19" t="inlineStr"/>
@@ -1800,7 +1910,8 @@
       </c>
       <c r="F40" s="19" t="inlineStr">
         <is>
-          <t>Annual Modern Slavery Statement, with case studies</t>
+          <t>We did not receive an end-2025 response for the related SP2030 target 11c(ii), so please include any relevant activity from across 2026.
+Annual Modern Slavery Statement, with case studies</t>
         </is>
       </c>
       <c r="G40" s="19" t="inlineStr">
@@ -1808,7 +1919,12 @@
           <t>We will draw on the annual Modern Slavery Statement and case studies to report on the University's approach to modern slavery and human rights risks (timing to be aligned with the Statement).</t>
         </is>
       </c>
-      <c r="H40" s="19" t="inlineStr"/>
+      <c r="H40" s="20" t="inlineStr">
+        <is>
+          <t>11c(ii)
+→ view SR25 response</t>
+        </is>
+      </c>
       <c r="I40" s="19" t="inlineStr"/>
       <c r="J40" s="19" t="inlineStr"/>
       <c r="K40" s="19" t="inlineStr"/>
@@ -1843,7 +1959,8 @@
       </c>
       <c r="F41" s="19" t="inlineStr">
         <is>
-          <t>Report on relevant sustainability-related investment portfolio metrics and report on how the University has complied with its related obligations</t>
+          <t>We did not receive an end-2025 response for the related SP2030 target 12b(i), so please include any relevant activity from across 2026.
+Report on relevant sustainability-related investment portfolio metrics and report on how the University has complied with its related obligations</t>
         </is>
       </c>
       <c r="G41" s="19" t="inlineStr">
@@ -1851,7 +1968,12 @@
           <t>We will report on sustainability-related investment portfolio metrics and the University's compliance with related obligations (e.g. UNPRI) in the Responsible investments section of the 2026 Sustainability Report.</t>
         </is>
       </c>
-      <c r="H41" s="19" t="inlineStr"/>
+      <c r="H41" s="20" t="inlineStr">
+        <is>
+          <t>12b(i)
+→ view SR25 response</t>
+        </is>
+      </c>
       <c r="I41" s="19" t="inlineStr"/>
       <c r="J41" s="19" t="inlineStr"/>
       <c r="K41" s="19" t="inlineStr"/>
@@ -1886,7 +2008,8 @@
       </c>
       <c r="F42" s="19" t="inlineStr">
         <is>
-          <t>Comment on living labs in the Faculty - outputs, outcomes, and impact</t>
+          <t>We did not receive an end-2025 response for the related SP2030 target 2a, so please include any relevant activity from across 2026.
+Comment on living labs in the Faculty - outputs, outcomes, and impact</t>
         </is>
       </c>
       <c r="G42" s="19" t="inlineStr">
@@ -1894,7 +2017,12 @@
           <t>We will share examples of living labs from across the University in the 2026 Sustainability Report, alongside CLLAP projects reported by CI&amp;S.</t>
         </is>
       </c>
-      <c r="H42" s="19" t="inlineStr"/>
+      <c r="H42" s="20" t="inlineStr">
+        <is>
+          <t>2a
+→ view SR25 response</t>
+        </is>
+      </c>
       <c r="I42" s="19" t="inlineStr"/>
       <c r="J42" s="19" t="inlineStr"/>
       <c r="K42" s="19" t="inlineStr"/>
@@ -1937,7 +2065,11 @@
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H43" s="19" t="inlineStr"/>
+      <c r="H43" s="19" t="inlineStr">
+        <is>
+          <t>N/A – new indicator</t>
+        </is>
+      </c>
       <c r="I43" s="19" t="inlineStr"/>
       <c r="J43" s="19" t="inlineStr"/>
       <c r="K43" s="19" t="inlineStr"/>
@@ -1980,7 +2112,11 @@
           <t>We will report on how sustainability is integrated into governance and decision-making across faculties and portfolios, and use responses as a baseline for the governance enabler from 2027.</t>
         </is>
       </c>
-      <c r="H44" s="19" t="inlineStr"/>
+      <c r="H44" s="19" t="inlineStr">
+        <is>
+          <t>N/A – new indicator</t>
+        </is>
+      </c>
       <c r="I44" s="19" t="inlineStr"/>
       <c r="J44" s="19" t="inlineStr"/>
       <c r="K44" s="19" t="inlineStr"/>
@@ -2022,6 +2158,14 @@
       <formula1>=Lists!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H16" location="'3. SR25 responses'!B24"/>
+    <hyperlink ref="H17" location="'3. SR25 responses'!B7"/>
+    <hyperlink ref="H32" location="'3. SR25 responses'!B23"/>
+    <hyperlink ref="H40" location="'3. SR25 responses'!B26"/>
+    <hyperlink ref="H41" location="'3. SR25 responses'!B27"/>
+    <hyperlink ref="H42" location="'3. SR25 responses'!B21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2072,7 +2216,7 @@
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Friday 4 December 2026 (TBC) (early submission helps us develop case studies).</t>
         </is>
@@ -2080,47 +2224,47 @@
     </row>
     <row r="6"/>
     <row r="8">
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="22" t="inlineStr"/>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr"/>
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr"/>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr"/>
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr"/>
+      <c r="F9" s="23" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
@@ -2369,4 +2513,743 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>End-2025 target status assessment and reporting (for reference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Your SR25 responses – Commercial, Infrastructure &amp; Sustainability (CI&amp;S)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>← Back to request</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>CD Development &amp; Estate Planning teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>SR25 ref</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>SP2030 target</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>2025 reporting request</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Confirmed end-2025 status</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>OPTION 1: Target-level reporting</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>OPTION 2: Indicator-level reporting</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Supporting information/comments</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>Related SR26 indicator(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="160" customHeight="1">
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>7b</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>The University has led or influenced discussions with precinct partners to further precinct-specific approaches to sustainability</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Case studies identifying the nature of the University’s involvement in sustainability issues for each precinct.</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr"/>
+      <c r="G7" s="19" t="inlineStr"/>
+      <c r="H7" s="19" t="inlineStr"/>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>EI1(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="160" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>8a(i)</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>The University reaches and maintains a 'high' climate change preparedness level</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Assessment based on the Climate Change Preparedness Framework</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr"/>
+      <c r="G8" s="19" t="inlineStr"/>
+      <c r="H8" s="19" t="inlineStr"/>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>CL3(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="160" customHeight="1">
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>8a(ii)</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>The University reaches and maintains a 'high' climate change preparedness level</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>Case studies demonstrating climate change preparedness activities in the Portfolio</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr"/>
+      <c r="G9" s="19" t="inlineStr"/>
+      <c r="H9" s="19" t="inlineStr"/>
+      <c r="I9" s="19" t="inlineStr"/>
+    </row>
+    <row r="10" ht="160" customHeight="1">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>9a(i)</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>Each campus achieves no net loss of biodiversity relative to defined baseline years by 2025</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Describe the impact of initiatives and projects (including the Estate Master Plan) on biodiversity</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr"/>
+      <c r="G10" s="19" t="inlineStr"/>
+      <c r="H10" s="19" t="inlineStr"/>
+      <c r="I10" s="19" t="inlineStr"/>
+    </row>
+    <row r="11" ht="160" customHeight="1">
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>10a(i)</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>The University has reduced total water consumption by 10% relative to a 2019 baseline</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>Describe efforts to reduce water use in development projects and estate planning activities</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr"/>
+      <c r="G11" s="19" t="inlineStr"/>
+      <c r="H11" s="19" t="inlineStr"/>
+      <c r="I11" s="19" t="inlineStr"/>
+    </row>
+    <row r="12" ht="160" customHeight="1">
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>10b(i)</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>The University has significantly increased the proportion of water consumption from non-potable sources compared to a 2019 baseline</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Describe efforts to increase non-potable water consumption in development projects and estate planning activities</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr"/>
+      <c r="G12" s="19" t="inlineStr"/>
+      <c r="H12" s="19" t="inlineStr"/>
+      <c r="I12" s="19" t="inlineStr"/>
+    </row>
+    <row r="13" ht="160" customHeight="1">
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>11a(i)</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>The University has reduced waste to landfill to 10kg per person</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Describe efforts to reduce and more effectively manage waste in development projects and estate planning activities</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr"/>
+      <c r="G13" s="19" t="inlineStr"/>
+      <c r="H13" s="19" t="inlineStr"/>
+      <c r="I13" s="19" t="inlineStr"/>
+    </row>
+    <row r="14" ht="160" customHeight="1">
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>11a(ii)</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>The University has reduced waste to landfill to 10kg per person</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>Mass of construction and demolition waste to landfill, disposed of via contractors on University construction projects</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr"/>
+      <c r="G14" s="19" t="inlineStr"/>
+      <c r="H14" s="19" t="inlineStr"/>
+      <c r="I14" s="19" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>CD Sustainability Strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>SR25 ref</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>SP2030 target</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>2025 reporting request</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>Confirmed end-2025 status</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>OPTION 1: Target-level reporting</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>OPTION 2: Indicator-level reporting</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>Supporting information/comments</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Related SR26 indicator(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="160" customHeight="1">
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>1a(i)</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>The University is certified carbon neutral by 2025</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>Comment on progress to reduce air travel emissions
+% change in air travel emissions in the Portfolio</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>Data request sent</t>
+        </is>
+      </c>
+      <c r="G18" s="19" t="inlineStr">
+        <is>
+          <t>The University has met its target of reducing flight emissions by 10%. Total GHG emissions in 2025 from flights was estimated to be 20,052 tCO2e whilst 2019 flight emissions were 27,044 tCO2e; approximately a 26% reduction in absolute emissions. 
+In terms of total distance flown, the University staff travelled 115,416,715 air kilometres in 2025; a 13% reduction compared with the 132,329,019 air kilometres flown in 2019.
+This achievement is attributable in part to  the "Air Travel Emissions Reduction Program", reduced travel budgets across the University, as well as improvements within the aviation industry such as newer fuel efficient air craft models being integrated into global fleets and lower carbon fuels being used.</t>
+        </is>
+      </c>
+      <c r="H18" s="19" t="inlineStr"/>
+      <c r="I18" s="19" t="inlineStr"/>
+    </row>
+    <row r="19" ht="160" customHeight="1">
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>1a(iI)</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>The University is certified carbon neutral by 2025</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>Progress towards attaining Climate Active carbon neutral certification</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="F19" s="19" t="inlineStr">
+        <is>
+          <t>Registered with Climate Active. Should be going ahead as planned.</t>
+        </is>
+      </c>
+      <c r="G19" s="19" t="inlineStr">
+        <is>
+          <t>The University is currently on track to being Climate Active Carbon Neutral certified for its 2025 Carbon Footprint. The University will be undergoing an assurance and technical assessment of its 2025 GHG inventory to as per Climate Active requirements, after which it submit all required document for certification. Notably, there can be a delay between the time of submission and actual approval of certification. The University will provide updates on this process as they become relevant.</t>
+        </is>
+      </c>
+      <c r="H19" s="19" t="inlineStr"/>
+      <c r="I19" s="19" t="inlineStr"/>
+    </row>
+    <row r="20" ht="160" customHeight="1">
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>1a(iii)</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>The University is certified carbon neutral by 2025</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Case studies and other knowledge mobilisation activities that enable 
+others to implement ambitious climate action</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>100% renewables - main story
+Supplier participation in providing data - reducing reported emissions based on actual emissions - mini case study. SBTI requirement into Keypath - option for case study [now working with suppliers to set 1.5 degree targets] - workshop with CD</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="inlineStr"/>
+      <c r="H20" s="19" t="inlineStr"/>
+      <c r="I20" s="19" t="inlineStr"/>
+    </row>
+    <row r="21" ht="160" customHeight="1">
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>2a</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>The University has curated living labs covering the priority areas of this Plan</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>Report on living labs at the University - outputs, outcomes and impact.</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr"/>
+      <c r="G21" s="19" t="inlineStr"/>
+      <c r="H21" s="19" t="inlineStr"/>
+      <c r="I21" s="19" t="inlineStr">
+        <is>
+          <t>EN1(b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="160" customHeight="1">
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>4b(ii)</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>Graduates have increased capabilities to shape, lead and succeed in the careers, communities and industries of sustainable societies (year on year).</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>Report on Mark Latham's project - as an example of a measure developed</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="inlineStr"/>
+      <c r="G22" s="19" t="inlineStr"/>
+      <c r="H22" s="19" t="inlineStr"/>
+      <c r="I22" s="19" t="inlineStr"/>
+    </row>
+    <row r="23" ht="160" customHeight="1">
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>5a(ii)</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>Sustainability research is integrated with campus operations and planning, to be an international exemplar of a sustainable community</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>Percentage of the University's research outputs that map to one or more SDGs in the top 10 per cent most cited in their field; Number of patent, policy and news/social media mentions for University research outputs mapped to SDGs</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="F23" s="19" t="inlineStr">
+        <is>
+          <t>Tangible improvement in some areas, but not all (haven't done ASRS, for example).</t>
+        </is>
+      </c>
+      <c r="G23" s="19" t="inlineStr"/>
+      <c r="H23" s="19" t="inlineStr"/>
+      <c r="I23" s="19" t="inlineStr">
+        <is>
+          <t>TR1(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="160" customHeight="1">
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>8a(i)</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>The University reaches and maintains a 'high' climate change preparedness level</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>Assessment based on the Climate Change Preparedness Framework</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="F24" s="19" t="inlineStr"/>
+      <c r="G24" s="19" t="inlineStr"/>
+      <c r="H24" s="19" t="inlineStr"/>
+      <c r="I24" s="19" t="inlineStr">
+        <is>
+          <t>CL3(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="160" customHeight="1">
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>8a(ii)</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>The University reaches and maintains a 'high' climate change preparedness level</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>Please provide commentary regarding the Portfolio/team's level of climate change preparedness. Refer to the Climate Change Preparedness Framework for guidance: https://www.unimelb.edu.au/sustainabilityreport/domain-3-walking-the-talk-in-our-operations/climate-resilience#progress-1</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="F25" s="19" t="inlineStr"/>
+      <c r="G25" s="19" t="inlineStr"/>
+      <c r="H25" s="19" t="inlineStr"/>
+      <c r="I25" s="19" t="inlineStr"/>
+    </row>
+    <row r="26" ht="160" customHeight="1">
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>11c(ii)</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>The University has principles for ethical and sustainable consumption and service provision embedded into operations and procurement practices</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>List of Fair Trade and other relevant third-party certifications</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="F26" s="19" t="inlineStr"/>
+      <c r="G26" s="19" t="inlineStr"/>
+      <c r="H26" s="19" t="inlineStr"/>
+      <c r="I26" s="19" t="inlineStr">
+        <is>
+          <t>MS1(a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="160" customHeight="1">
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>12b(i)</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>Enhanced transparent reporting of the University’s investment portfolio</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>Report on relevant sustainability-related investment portfolio metrics, including carbon intensity</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="F27" s="19" t="inlineStr"/>
+      <c r="G27" s="19" t="inlineStr"/>
+      <c r="H27" s="19" t="inlineStr"/>
+      <c r="I27" s="19" t="inlineStr">
+        <is>
+          <t>RI1(b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="160" customHeight="1">
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>12b(ii)</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>Enhanced transparent reporting of the University’s investment portfolio</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>Reporting on how the University has complied with its related obligations</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="F28" s="19" t="inlineStr"/>
+      <c r="G28" s="19" t="inlineStr"/>
+      <c r="H28" s="19" t="inlineStr"/>
+      <c r="I28" s="19" t="inlineStr"/>
+    </row>
+    <row r="29" ht="160" customHeight="1">
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>11a(ii)</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>The University has reduced waste to landfill to 10kg per person</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>Mass of construction and demolition waste to landfill, disposed of via contractors on University construction projects (Gerard to supply for major projects)</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="F29" s="19" t="inlineStr"/>
+      <c r="G29" s="19" t="inlineStr"/>
+      <c r="H29" s="19" t="inlineStr"/>
+      <c r="I29" s="19" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:I3"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B4" location="'1. Reporting template'!A1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/central_unit_requests/CIandS - end-2026 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/CIandS - end-2026 sustainability reporting request.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Reporting template" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. OPTIONAL highlighted stories" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. SR25 responses" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. SR25 responses" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Quantitative data" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,8 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="20">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.##"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,7 +48,14 @@
     <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
-      <sz val="16"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <color rgb="000E2841"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -54,13 +64,29 @@
       <sz val="12"/>
     </font>
     <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="000E2841"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Aptos Narrow"/>
-      <sz val="11"/>
+      <b val="1"/>
+      <sz val="16"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -97,26 +123,8 @@
     <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <b val="1"/>
-      <color rgb="000E2841"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <b val="1"/>
       <color rgb="000E2841"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="000E2841"/>
-      <sz val="12"/>
     </font>
     <font>
       <name val="Aptos Narrow"/>
@@ -135,17 +143,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="000B3040"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C1E4F5"/>
+        <fgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -155,7 +163,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
+        <fgColor rgb="00C1E4F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -191,63 +199,81 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -928,7 +954,8 @@
       <c r="F16" s="19" t="inlineStr">
         <is>
           <t>We did not receive an end-2025 response for the related SP2030 target 8a(i), so please include any relevant activity from across 2026.
-Provide update of University maturity assesment. Include maturity ratings, key gaps and priority improvement actions.when available</t>
+Provide update of University maturity assesment. Include maturity ratings, key gaps and priority improvement actions.when available
+Quantitative figures for this indicator are requested separately in Tab 4 (Quantitative data).</t>
         </is>
       </c>
       <c r="G16" s="19" t="inlineStr">
@@ -2009,7 +2036,8 @@
       <c r="F42" s="19" t="inlineStr">
         <is>
           <t>We did not receive an end-2025 response for the related SP2030 target 2a, so please include any relevant activity from across 2026.
-Comment on living labs in the Faculty - outputs, outcomes, and impact</t>
+Comment on living labs in the Faculty - outputs, outcomes, and impact
+Quantitative figures for this indicator are requested separately in Tab 4 (Quantitative data).</t>
         </is>
       </c>
       <c r="G42" s="19" t="inlineStr">
@@ -2310,217 +2338,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>End 2026 target status</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Data owner confirms</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Request status</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Y/N</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Target status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Response count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Please select from dropdown</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Not sent</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Sent</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Partially – see comments</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Chased</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Support meeting</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Under review</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Not required</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3252,4 +3069,697 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>End-2026 target status assessment and reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Quantitative data – Commercial, Infrastructure &amp; Sustainability (CI&amp;S)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t>These figures feed the Sustainability Databook (the University's authoritative quantitative source). Previous years are shown for context – please do not alter. Please provide the CY2026 value (provisional figures are fine; we will confirm final figures with you in February), the data source, and any change to definition or boundary. Due: Friday 15 January 2027 (TBC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Context only (please do not alter)</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>Please fill in these cells</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Indicator</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>CY2023</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>CY2024</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>CY2025</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>Data status</t>
+        </is>
+      </c>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>CY2026 value</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
+          <t>Data source (file name, link or system)</t>
+        </is>
+      </c>
+      <c r="M6" s="15" t="inlineStr">
+        <is>
+          <t>Change to definition or boundary?</t>
+        </is>
+      </c>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t>Notes / limitations</t>
+        </is>
+      </c>
+      <c r="O6" s="15" t="inlineStr">
+        <is>
+          <t>Useful case studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>No instructions – context only.</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr"/>
+      <c r="D7" s="26" t="inlineStr"/>
+      <c r="E7" s="26" t="inlineStr"/>
+      <c r="F7" s="26" t="inlineStr"/>
+      <c r="G7" s="26" t="inlineStr"/>
+      <c r="H7" s="26" t="inlineStr"/>
+      <c r="I7" s="26" t="inlineStr"/>
+      <c r="J7" s="26" t="inlineStr"/>
+      <c r="K7" s="26" t="inlineStr">
+        <is>
+          <t>Please enter numerical values</t>
+        </is>
+      </c>
+      <c r="L7" s="26" t="inlineStr">
+        <is>
+          <t>Please provide a file name or link to the data source</t>
+        </is>
+      </c>
+      <c r="M7" s="26" t="inlineStr">
+        <is>
+          <t>Describe any change since last year (or 'No change')</t>
+        </is>
+      </c>
+      <c r="N7" s="26" t="inlineStr">
+        <is>
+          <t>Please add any additional notes here</t>
+        </is>
+      </c>
+      <c r="O7" s="26" t="inlineStr">
+        <is>
+          <t>Please provide information on any useful case studies</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>CL3(a)</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>Maturity assessment of the University's preparedness for climate-related impacts and capability to respond</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>Average Total Maturity Score</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="28" t="n"/>
+      <c r="H8" s="28" t="n"/>
+      <c r="I8" s="28" t="n"/>
+      <c r="J8" s="27" t="inlineStr"/>
+      <c r="K8" s="29" t="n"/>
+      <c r="L8" s="29" t="n"/>
+      <c r="M8" s="29" t="n"/>
+      <c r="N8" s="29" t="n"/>
+      <c r="O8" s="29" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>CL3(a)</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr"/>
+      <c r="D9" s="30" t="inlineStr">
+        <is>
+          <t>Maturitu Score - Governance and strategy</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr"/>
+      <c r="F9" s="31" t="n"/>
+      <c r="G9" s="31" t="n"/>
+      <c r="H9" s="31" t="n"/>
+      <c r="I9" s="31" t="n"/>
+      <c r="J9" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K9" s="19" t="n"/>
+      <c r="L9" s="19" t="n"/>
+      <c r="M9" s="19" t="n"/>
+      <c r="N9" s="19" t="n"/>
+      <c r="O9" s="19" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>CL3(a)</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr"/>
+      <c r="D10" s="30" t="inlineStr">
+        <is>
+          <t>Maturity Score - Health and safety</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr"/>
+      <c r="F10" s="31" t="n"/>
+      <c r="G10" s="31" t="n"/>
+      <c r="H10" s="31" t="n"/>
+      <c r="I10" s="31" t="n"/>
+      <c r="J10" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K10" s="19" t="n"/>
+      <c r="L10" s="19" t="n"/>
+      <c r="M10" s="19" t="n"/>
+      <c r="N10" s="19" t="n"/>
+      <c r="O10" s="19" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>CL3(a)</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr"/>
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>Maturity Score - Business continuity</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr"/>
+      <c r="F11" s="31" t="n"/>
+      <c r="G11" s="31" t="n"/>
+      <c r="H11" s="31" t="n"/>
+      <c r="I11" s="31" t="n"/>
+      <c r="J11" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K11" s="19" t="n"/>
+      <c r="L11" s="19" t="n"/>
+      <c r="M11" s="19" t="n"/>
+      <c r="N11" s="19" t="n"/>
+      <c r="O11" s="19" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>CL3(a)</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr"/>
+      <c r="D12" s="30" t="inlineStr">
+        <is>
+          <t>Maturity Score - Emergency management and critical incidence management</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="31" t="n"/>
+      <c r="H12" s="31" t="n"/>
+      <c r="I12" s="31" t="n"/>
+      <c r="J12" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K12" s="19" t="n"/>
+      <c r="L12" s="19" t="n"/>
+      <c r="M12" s="19" t="n"/>
+      <c r="N12" s="19" t="n"/>
+      <c r="O12" s="19" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>CL3(a)</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr"/>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>Maturity Score - Estate and buildings</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr"/>
+      <c r="F13" s="31" t="n"/>
+      <c r="G13" s="31" t="n"/>
+      <c r="H13" s="31" t="n"/>
+      <c r="I13" s="31" t="n"/>
+      <c r="J13" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K13" s="19" t="n"/>
+      <c r="L13" s="19" t="n"/>
+      <c r="M13" s="19" t="n"/>
+      <c r="N13" s="19" t="n"/>
+      <c r="O13" s="19" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>CL3(a)</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr"/>
+      <c r="D14" s="30" t="inlineStr">
+        <is>
+          <t>Maturity Score - Water management</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr"/>
+      <c r="F14" s="31" t="n"/>
+      <c r="G14" s="31" t="n"/>
+      <c r="H14" s="31" t="n"/>
+      <c r="I14" s="31" t="n"/>
+      <c r="J14" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K14" s="19" t="n"/>
+      <c r="L14" s="19" t="n"/>
+      <c r="M14" s="19" t="n"/>
+      <c r="N14" s="19" t="n"/>
+      <c r="O14" s="19" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>CL3(a)</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr"/>
+      <c r="D15" s="30" t="inlineStr">
+        <is>
+          <t>Maturity Score - Financial planning and reporting</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr"/>
+      <c r="F15" s="31" t="n"/>
+      <c r="G15" s="31" t="n"/>
+      <c r="H15" s="31" t="n"/>
+      <c r="I15" s="31" t="n"/>
+      <c r="J15" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K15" s="19" t="n"/>
+      <c r="L15" s="19" t="n"/>
+      <c r="M15" s="19" t="n"/>
+      <c r="N15" s="19" t="n"/>
+      <c r="O15" s="19" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>EN1(b)</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Living laboratories enabling applied learning, research and operational sustainability outcomes</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Number of projects funded (CLLAP)</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="n"/>
+      <c r="G16" s="31" t="n"/>
+      <c r="H16" s="31" t="n"/>
+      <c r="I16" s="31" t="n"/>
+      <c r="J16" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K16" s="19" t="n"/>
+      <c r="L16" s="19" t="n"/>
+      <c r="M16" s="19" t="n"/>
+      <c r="N16" s="19" t="n"/>
+      <c r="O16" s="19" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>EN1(b)</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr"/>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>Total funding for projects</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="n"/>
+      <c r="G17" s="31" t="n"/>
+      <c r="H17" s="31" t="n"/>
+      <c r="I17" s="31" t="n"/>
+      <c r="J17" s="19" t="inlineStr">
+        <is>
+          <t>New – no data yet</t>
+        </is>
+      </c>
+      <c r="K17" s="19" t="n"/>
+      <c r="L17" s="19" t="n"/>
+      <c r="M17" s="19" t="n"/>
+      <c r="N17" s="19" t="n"/>
+      <c r="O17" s="19" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B3:O3"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="K5:O5"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="M8:M18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
+      <formula1>"No change,Yes – see notes"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>End 2026 target status</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Data owner confirms</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Request status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Y/N</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Target status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Response count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Please select from dropdown</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Met or exceeded</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sent</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Partially – see comments</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Chased</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Not met</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Not met</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Support meeting</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Not yet started</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Not yet started</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Under review</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Not required</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>